--- a/data/2026_05终端回收.xlsx
+++ b/data/2026_05终端回收.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="139">
   <si>
     <t>用户号码</t>
   </si>
@@ -47,12 +47,30 @@
     <t>工程师姓名</t>
   </si>
   <si>
+    <t>工程师姓名（区分反馈）</t>
+  </si>
+  <si>
+    <t>工程师所属营服（区分反馈）</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>详情说明</t>
   </si>
   <si>
+    <t>工单下发归类</t>
+  </si>
+  <si>
     <t>用户名称</t>
   </si>
   <si>
+    <t>宽带账号</t>
+  </si>
+  <si>
+    <t>接入间编码</t>
+  </si>
+  <si>
     <t>接入间名称</t>
   </si>
   <si>
@@ -83,15 +101,21 @@
     <t>用户地址</t>
   </si>
   <si>
+    <t>用户地址（更正）</t>
+  </si>
+  <si>
+    <t>定位地址</t>
+  </si>
+  <si>
+    <t>实际距离(米)</t>
+  </si>
+  <si>
     <t>是否上门</t>
   </si>
   <si>
     <t>是否张贴公告</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>是否回收设备</t>
   </si>
   <si>
@@ -119,9 +143,51 @@
     <t>其中已移交TTR主光猫数量</t>
   </si>
   <si>
+    <t>回收设备</t>
+  </si>
+  <si>
+    <t>光猫（实物系统）</t>
+  </si>
+  <si>
+    <t>光猫移交情况</t>
+  </si>
+  <si>
+    <t>路由器</t>
+  </si>
+  <si>
+    <t>路由器移交情况</t>
+  </si>
+  <si>
+    <t>FTTR主</t>
+  </si>
+  <si>
+    <t>FTTR主移交情况</t>
+  </si>
+  <si>
+    <t>FTTR从</t>
+  </si>
+  <si>
+    <t>FTTR从移交情况</t>
+  </si>
+  <si>
+    <t>IPTV</t>
+  </si>
+  <si>
+    <t>IPTV移交情况</t>
+  </si>
+  <si>
+    <t>OTT</t>
+  </si>
+  <si>
+    <t>OTT移交情况</t>
+  </si>
+  <si>
     <t>周久翔</t>
   </si>
   <si>
+    <t>南沙中</t>
+  </si>
+  <si>
     <t>宽带号码：02001559573；装机地址：广州市南沙区黄阁镇莲溪村麒龙西路荔园巷8横10号303房；回收终端：2台  光猫_ZTEGD5A901D3、组网_D8EF42311DC5</t>
   </si>
   <si>
@@ -131,6 +197,12 @@
     <t>龙高峰</t>
   </si>
   <si>
+    <t>GZFTH4230328663138304@16900.gd</t>
+  </si>
+  <si>
+    <t>GZNS0490</t>
+  </si>
+  <si>
     <t>广州南沙黄阁大塘村(FTTH)ZZ</t>
   </si>
   <si>
@@ -167,6 +239,12 @@
     <t>陆敏健</t>
   </si>
   <si>
+    <t>GZFTH4427176694521856@16900.gd</t>
+  </si>
+  <si>
+    <t>GZNS0919</t>
+  </si>
+  <si>
     <t>广州南沙时代天逸二期(FTTH)XG</t>
   </si>
   <si>
@@ -197,6 +275,12 @@
     <t>王铮</t>
   </si>
   <si>
+    <t>GZFTH543311328321536@16900.gd</t>
+  </si>
+  <si>
+    <t>GZNS0483</t>
+  </si>
+  <si>
     <t>广州南沙莲溪村北(FTTH)ZZ</t>
   </si>
   <si>
@@ -224,6 +308,9 @@
     <t>洪俊贤</t>
   </si>
   <si>
+    <t>GZFTH5993213294747648@16900.gd</t>
+  </si>
+  <si>
     <t>南沙金洲社区综合营服小CEO</t>
   </si>
   <si>
@@ -245,6 +332,12 @@
     <t>蒋永铭</t>
   </si>
   <si>
+    <t>GZFTH687969617666048@16900.gd</t>
+  </si>
+  <si>
+    <t>GZNS0655</t>
+  </si>
+  <si>
     <t>广州南沙南沙水恋(FTTH)</t>
   </si>
   <si>
@@ -263,6 +356,9 @@
     <t>杨柱良</t>
   </si>
   <si>
+    <t>GZFTH6938431121367040@16900.gd</t>
+  </si>
+  <si>
     <t>邓日荣</t>
   </si>
   <si>
@@ -281,6 +377,9 @@
     <t>麦镇标</t>
   </si>
   <si>
+    <t>GZFTH7300050666815488@16900.gd</t>
+  </si>
+  <si>
     <t>南沙金洲营业厅</t>
   </si>
   <si>
@@ -302,6 +401,9 @@
     <t>杨静</t>
   </si>
   <si>
+    <t>GZFTH9123909140332544@16900.gd</t>
+  </si>
+  <si>
     <t>W南沙线上交付嘉音讯互联网融合</t>
   </si>
   <si>
@@ -320,6 +422,9 @@
     <t>李伟铭</t>
   </si>
   <si>
+    <t>GZFTH956951996579840@16900.gd</t>
+  </si>
+  <si>
     <t>广州市南沙区黄阁镇大塘村崇俭巷21号|||||***</t>
   </si>
   <si>
@@ -333,6 +438,9 @@
   </si>
   <si>
     <t>彭加保</t>
+  </si>
+  <si>
+    <t>GZFTH9679576571895808@16900.gd</t>
   </si>
   <si>
     <t>广州市南沙区黄阁镇莲溪村新丰二巷5号101</t>
@@ -560,13 +668,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1022,7 +1130,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1053,28 +1161,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1603,7 +1723,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:BH11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -1615,930 +1735,1381 @@
     <col min="23" max="23" width="64.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="54" spans="1:30">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" ht="54" spans="1:60">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="N1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="O1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="P1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="R1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="U1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="V1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="W1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="X1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Y1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="Z1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="AA1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="AB1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="AC1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="AD1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="13" t="s">
+      <c r="AE1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="13" t="s">
+      <c r="AF1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="13" t="s">
+      <c r="AG1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="13" t="s">
+      <c r="AH1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="16" t="s">
+      <c r="AI1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="AJ1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="16" t="s">
+      <c r="AK1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="16" t="s">
+      <c r="AL1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM1" s="17" t="s">
         <v>28</v>
       </c>
+      <c r="AN1" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="AO1" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP1" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="AQ1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="AS1" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT1" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="AU1" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV1" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW1" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="AX1" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="AY1" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="AZ1" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="BA1" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="BB1" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="BC1" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="BD1" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="BE1" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="BF1" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="BG1" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="BH1" s="20" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="2" ht="33" spans="1:30">
-      <c r="A2" s="5">
+    <row r="2" ht="33" spans="1:60">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="5">
         <v>13711666681</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7">
+      <c r="J2" s="6"/>
+      <c r="K2" s="7">
         <v>18520034201</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14" t="s">
-        <v>40</v>
+      <c r="L2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="12"/>
+      <c r="S2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="W2" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="X2" s="15">
+        <v>57</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y2" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA2" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB2" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD2" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG2" s="18"/>
+      <c r="AH2" s="18"/>
+      <c r="AI2" s="18"/>
+      <c r="AJ2" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK2" s="18"/>
+      <c r="AL2" s="18"/>
+      <c r="AM2" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO2" s="21">
         <v>2</v>
       </c>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="14">
-        <v>0</v>
-      </c>
+      <c r="AP2" s="8"/>
+      <c r="AQ2" s="11"/>
+      <c r="AR2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="18"/>
+      <c r="AW2" s="18"/>
+      <c r="AX2" s="18"/>
+      <c r="AY2" s="18"/>
+      <c r="AZ2" s="18"/>
+      <c r="BA2" s="18"/>
+      <c r="BB2" s="18"/>
+      <c r="BC2" s="18"/>
+      <c r="BD2" s="18"/>
+      <c r="BE2" s="18"/>
+      <c r="BF2" s="18"/>
+      <c r="BG2" s="18"/>
+      <c r="BH2" s="18"/>
     </row>
-    <row r="3" ht="82.5" spans="1:30">
-      <c r="A3" s="5">
+    <row r="3" ht="82.5" spans="1:60">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="5">
         <v>13265088078</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="7">
+      <c r="J3" s="6"/>
+      <c r="K3" s="7">
         <v>18520034201</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="S3" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14" t="s">
-        <v>40</v>
+      <c r="M3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="12"/>
+      <c r="S3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="U3" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="W3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y3" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z3" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB3" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC3" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD3" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF3" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG3" s="18"/>
+      <c r="AH3" s="18"/>
+      <c r="AI3" s="18"/>
+      <c r="AJ3" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK3" s="18"/>
+      <c r="AL3" s="18"/>
+      <c r="AM3" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN3" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO3" s="21">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="8"/>
+      <c r="AQ3" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="18"/>
+      <c r="AW3" s="18"/>
+      <c r="AX3" s="18"/>
+      <c r="AY3" s="18"/>
+      <c r="AZ3" s="18"/>
+      <c r="BA3" s="18"/>
+      <c r="BB3" s="18"/>
+      <c r="BC3" s="18"/>
+      <c r="BD3" s="18"/>
+      <c r="BE3" s="18"/>
+      <c r="BF3" s="18"/>
+      <c r="BG3" s="18"/>
+      <c r="BH3" s="18"/>
+    </row>
+    <row r="4" ht="49.5" spans="1:60">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="5">
+        <v>18939223553</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="7">
+        <v>18520034201</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O4" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="X3" s="15">
+      <c r="P4" s="11"/>
+      <c r="Q4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="R4" s="12"/>
+      <c r="S4" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="U4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y4" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA4" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD4" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE4" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="AG4" s="18"/>
+      <c r="AH4" s="18"/>
+      <c r="AI4" s="18"/>
+      <c r="AJ4" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK4" s="18"/>
+      <c r="AL4" s="18"/>
+      <c r="AM4" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN4" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO4" s="21">
         <v>2</v>
       </c>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="17">
+      <c r="AP4" s="8"/>
+      <c r="AQ4" s="11"/>
+      <c r="AR4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV4" s="18"/>
+      <c r="AW4" s="18"/>
+      <c r="AX4" s="18"/>
+      <c r="AY4" s="18"/>
+      <c r="AZ4" s="18"/>
+      <c r="BA4" s="18"/>
+      <c r="BB4" s="18"/>
+      <c r="BC4" s="18"/>
+      <c r="BD4" s="18"/>
+      <c r="BE4" s="18"/>
+      <c r="BF4" s="18"/>
+      <c r="BG4" s="18"/>
+      <c r="BH4" s="18"/>
+    </row>
+    <row r="5" ht="66" spans="1:60">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="5">
+        <v>13622829697</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="7">
+        <v>18520034201</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="R5" s="12"/>
+      <c r="S5" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="U5" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC5" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AD5" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF5" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG5" s="18"/>
+      <c r="AH5" s="18"/>
+      <c r="AI5" s="18"/>
+      <c r="AJ5" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK5" s="18"/>
+      <c r="AL5" s="18"/>
+      <c r="AM5" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO5" s="21">
+        <v>3</v>
+      </c>
+      <c r="AP5" s="8"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV5" s="18"/>
+      <c r="AW5" s="18"/>
+      <c r="AX5" s="18"/>
+      <c r="AY5" s="18"/>
+      <c r="AZ5" s="18"/>
+      <c r="BA5" s="18"/>
+      <c r="BB5" s="18"/>
+      <c r="BC5" s="18"/>
+      <c r="BD5" s="18"/>
+      <c r="BE5" s="18"/>
+      <c r="BF5" s="18"/>
+      <c r="BG5" s="18"/>
+      <c r="BH5" s="18"/>
+    </row>
+    <row r="6" ht="33" spans="1:60">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="5">
+        <v>18634300024</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="7">
+        <v>18520034201</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="R6" s="12"/>
+      <c r="S6" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="T6" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="U6" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="X6" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB6" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC6" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD6" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE6" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF6" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="AG6" s="18"/>
+      <c r="AH6" s="18"/>
+      <c r="AI6" s="18"/>
+      <c r="AJ6" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK6" s="18"/>
+      <c r="AL6" s="18"/>
+      <c r="AM6" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN6" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO6" s="21">
+        <v>2</v>
+      </c>
+      <c r="AP6" s="8"/>
+      <c r="AQ6" s="11">
         <v>1</v>
       </c>
-      <c r="AA3" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="14">
-        <v>0</v>
-      </c>
+      <c r="AR6" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="18"/>
+      <c r="AW6" s="18"/>
+      <c r="AX6" s="18"/>
+      <c r="AY6" s="18"/>
+      <c r="AZ6" s="18"/>
+      <c r="BA6" s="18"/>
+      <c r="BB6" s="18"/>
+      <c r="BC6" s="18"/>
+      <c r="BD6" s="18"/>
+      <c r="BE6" s="18"/>
+      <c r="BF6" s="18"/>
+      <c r="BG6" s="18"/>
+      <c r="BH6" s="18"/>
     </row>
-    <row r="4" ht="49.5" spans="1:30">
-      <c r="A4" s="5">
-        <v>18939223553</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="7">
+    <row r="7" ht="33" spans="1:60">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="5">
+        <v>18520611583</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="7">
         <v>18520034201</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="11" t="s">
+      <c r="L7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="R7" s="12"/>
+      <c r="S7" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="U7" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="V7" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="W7" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="X7" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="N4" s="11" t="s">
+      <c r="Y7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB7" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC7" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD7" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF7" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="AG7" s="18"/>
+      <c r="AH7" s="18"/>
+      <c r="AI7" s="18"/>
+      <c r="AJ7" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK7" s="18"/>
+      <c r="AL7" s="18"/>
+      <c r="AM7" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO7" s="21">
+        <v>2</v>
+      </c>
+      <c r="AP7" s="8"/>
+      <c r="AQ7" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV7" s="18"/>
+      <c r="AW7" s="18"/>
+      <c r="AX7" s="18"/>
+      <c r="AY7" s="18"/>
+      <c r="AZ7" s="18"/>
+      <c r="BA7" s="18"/>
+      <c r="BB7" s="18"/>
+      <c r="BC7" s="18"/>
+      <c r="BD7" s="18"/>
+      <c r="BE7" s="18"/>
+      <c r="BF7" s="18"/>
+      <c r="BG7" s="18"/>
+      <c r="BH7" s="18"/>
+    </row>
+    <row r="8" ht="33" spans="1:60">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="5">
+        <v>18675850663</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="7">
+        <v>18520034201</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="R8" s="12"/>
+      <c r="S8" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="T8" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="U8" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="X8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC8" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="AE8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AG8" s="18"/>
+      <c r="AH8" s="18"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK8" s="18"/>
+      <c r="AL8" s="18"/>
+      <c r="AM8" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN8" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="AO8" s="21">
+        <v>2</v>
+      </c>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR8" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="18"/>
+      <c r="AW8" s="18"/>
+      <c r="AX8" s="18"/>
+      <c r="AY8" s="18"/>
+      <c r="AZ8" s="18"/>
+      <c r="BA8" s="18"/>
+      <c r="BB8" s="18"/>
+      <c r="BC8" s="18"/>
+      <c r="BD8" s="18"/>
+      <c r="BE8" s="18"/>
+      <c r="BF8" s="18"/>
+      <c r="BG8" s="18"/>
+      <c r="BH8" s="18"/>
+    </row>
+    <row r="9" ht="66" spans="1:60">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="5">
+        <v>16626725286</v>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="7">
+        <v>18520034201</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="R9" s="12"/>
+      <c r="S9" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="U9" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="X9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC9" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD9" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="AE9" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF9" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG9" s="18"/>
+      <c r="AH9" s="18"/>
+      <c r="AI9" s="18"/>
+      <c r="AJ9" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK9" s="18"/>
+      <c r="AL9" s="18"/>
+      <c r="AM9" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN9" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AO9" s="21">
+        <v>2</v>
+      </c>
+      <c r="AP9" s="8"/>
+      <c r="AQ9" s="11"/>
+      <c r="AR9" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV9" s="18"/>
+      <c r="AW9" s="18"/>
+      <c r="AX9" s="18"/>
+      <c r="AY9" s="18"/>
+      <c r="AZ9" s="18"/>
+      <c r="BA9" s="18"/>
+      <c r="BB9" s="18"/>
+      <c r="BC9" s="18"/>
+      <c r="BD9" s="18"/>
+      <c r="BE9" s="18"/>
+      <c r="BF9" s="18"/>
+      <c r="BG9" s="18"/>
+      <c r="BH9" s="18"/>
+    </row>
+    <row r="10" ht="33" spans="1:60">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="5">
+        <v>18675828062</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="7">
+        <v>18520034201</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="R10" s="12"/>
+      <c r="S10" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="T10" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="U10" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="W10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q4" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="8" t="s">
+      <c r="X10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y10" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="S4" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W4" s="8" t="s">
+      <c r="Z10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC10" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="X4" s="15">
-        <v>2</v>
-      </c>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="17"/>
-      <c r="AA4" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="14">
-        <v>0</v>
-      </c>
+      <c r="AD10" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF10" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG10" s="18"/>
+      <c r="AH10" s="18"/>
+      <c r="AI10" s="18"/>
+      <c r="AJ10" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK10" s="18"/>
+      <c r="AL10" s="18"/>
+      <c r="AM10" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN10" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="AO10" s="21">
+        <v>3</v>
+      </c>
+      <c r="AP10" s="21"/>
+      <c r="AQ10" s="11"/>
+      <c r="AR10" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="18"/>
+      <c r="AW10" s="18"/>
+      <c r="AX10" s="18"/>
+      <c r="AY10" s="18"/>
+      <c r="AZ10" s="18"/>
+      <c r="BA10" s="18"/>
+      <c r="BB10" s="18"/>
+      <c r="BC10" s="18"/>
+      <c r="BD10" s="18"/>
+      <c r="BE10" s="18"/>
+      <c r="BF10" s="18"/>
+      <c r="BG10" s="18"/>
+      <c r="BH10" s="18"/>
     </row>
-    <row r="5" ht="66" spans="1:30">
-      <c r="A5" s="5">
-        <v>13622829697</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="7">
+    <row r="11" ht="49.5" spans="1:60">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="5">
+        <v>13926256389</v>
+      </c>
+      <c r="J11" s="6"/>
+      <c r="K11" s="7">
         <v>18520034201</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="L11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="R11" s="12"/>
+      <c r="S11" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="T11" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="U11" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="X11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB11" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC11" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AD11" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AE11" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="H5" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O5" s="11" t="s">
+      <c r="AF11" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG11" s="18"/>
+      <c r="AH11" s="18"/>
+      <c r="AI11" s="18"/>
+      <c r="AJ11" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="P5" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="S5" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W5" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="X5" s="15">
-        <v>3</v>
-      </c>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="33" spans="1:30">
-      <c r="A6" s="5">
-        <v>18634300024</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="7">
-        <v>18520034201</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="P6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="S6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W6" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="X6" s="15">
-        <v>2</v>
-      </c>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="17">
+      <c r="AK11" s="18"/>
+      <c r="AL11" s="18"/>
+      <c r="AM11" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN11" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AO11" s="21">
         <v>1</v>
       </c>
-      <c r="AA6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="33" spans="1:30">
-      <c r="A7" s="5">
-        <v>18520611583</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7">
-        <v>18520034201</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="P7" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R7" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="S7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W7" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="X7" s="15">
-        <v>2</v>
-      </c>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="33" spans="1:30">
-      <c r="A8" s="5">
-        <v>18675850663</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="7">
-        <v>18520034201</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="P8" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="S8" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="X8" s="15">
-        <v>2</v>
-      </c>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="66" spans="1:30">
-      <c r="A9" s="5">
-        <v>16626725286</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="7">
-        <v>18520034201</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N9" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="P9" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R9" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="S9" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W9" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="X9" s="15">
-        <v>2</v>
-      </c>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="33" spans="1:30">
-      <c r="A10" s="5">
-        <v>18675828062</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="7">
-        <v>18520034201</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N10" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="P10" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R10" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="S10" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W10" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="X10" s="15">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="15"/>
-      <c r="Z10" s="17"/>
-      <c r="AA10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="49.5" spans="1:30">
-      <c r="A11" s="5">
-        <v>13926256389</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="7">
-        <v>18520034201</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="N11" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="P11" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q11" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R11" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="S11" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="W11" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="X11" s="15">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="14">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="14">
-        <v>0</v>
-      </c>
+      <c r="AP11" s="21"/>
+      <c r="AQ11" s="11"/>
+      <c r="AR11" s="18">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="18">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="18">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="18">
+        <v>0</v>
+      </c>
+      <c r="AV11" s="18"/>
+      <c r="AW11" s="18"/>
+      <c r="AX11" s="18"/>
+      <c r="AY11" s="18"/>
+      <c r="AZ11" s="18"/>
+      <c r="BA11" s="18"/>
+      <c r="BB11" s="18"/>
+      <c r="BC11" s="18"/>
+      <c r="BD11" s="18"/>
+      <c r="BE11" s="18"/>
+      <c r="BF11" s="18"/>
+      <c r="BG11" s="18"/>
+      <c r="BH11" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AD11" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
